--- a/satisfaction_surveys/006_national_security_expert_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/006_national_security_expert_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -822,8 +822,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -851,12 +851,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'security_manager'}</t>
+          <t>security_manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Security Manager'}</t>
+          <t>Security Manager</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'security_analyst'}</t>
+          <t>security_analyst</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Security Analyst'}</t>
+          <t>Security Analyst</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'security_consultant'}</t>
+          <t>security_consultant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Security Consultant'}</t>
+          <t>Security Consultant</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'security_specialist'}</t>
+          <t>security_specialist</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Security Specialist'}</t>
+          <t>Security Specialist</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'security_manager'}</t>
+          <t>security_manager</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Security Manager'}</t>
+          <t>Security Manager</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'security_analyst'}</t>
+          <t>security_analyst</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Security Analyst'}</t>
+          <t>Security Analyst</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'security_consultant'}</t>
+          <t>security_consultant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Security Consultant'}</t>
+          <t>Security Consultant</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'In-Person'}</t>
+          <t>In-Person</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'In-Person'}</t>
+          <t>In-Person</t>
         </is>
       </c>
     </row>
